--- a/data/trans_camb/P3A_R2-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P3A_R2-Habitat-trans_camb.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares en los que las tareas domésticas las realiza principalmente una persona con remuneración</t>
+          <t>Hogares en los que las tareas domésticas las realiza principalmente una persona con remuneración (por ingresos del hogar o no)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,3; 4,01</t>
+          <t>0,47; 3,93</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,79; 1,14</t>
+          <t>-1,91; 1,07</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,27; 6,3</t>
+          <t>2,17; 6,24</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,12; 4,03</t>
+          <t>0,21; 3,99</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 2,71</t>
+          <t>-0,87; 2,75</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,51; 6,28</t>
+          <t>2,59; 6,19</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,68; 3,5</t>
+          <t>0,81; 3,28</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 1,48</t>
+          <t>-0,8; 1,48</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,97; 5,49</t>
+          <t>3,0; 5,59</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>8,06; 276,16</t>
+          <t>10,34; 277,69</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-61,32; 84,41</t>
+          <t>-62,24; 76,29</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>66,88; 417,33</t>
+          <t>60,3; 414,51</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,26; 298,43</t>
+          <t>3,59; 282,62</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-30,07; 207,58</t>
+          <t>-35,84; 209,11</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>77,6; 488,82</t>
+          <t>85,29; 494,52</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>23,54; 213,61</t>
+          <t>30,56; 205,93</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-32,7; 98,44</t>
+          <t>-30,98; 88,52</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>102,6; 341,9</t>
+          <t>107,22; 345,35</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,18; 2,46</t>
+          <t>-1,36; 2,38</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,17; 0,04</t>
+          <t>-3,19; -0,02</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,78; 1,22</t>
+          <t>-3,07; 1,15</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,9; 4,01</t>
+          <t>0,94; 4,1</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 2,35</t>
+          <t>-0,47; 2,41</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,02; 4,82</t>
+          <t>2,14; 4,98</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,32; 2,75</t>
+          <t>0,35; 2,81</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 0,81</t>
+          <t>-1,36; 0,76</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-0,28; 2,49</t>
+          <t>-0,24; 2,5</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-29,32; 93,23</t>
+          <t>-30,83; 86,25</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-68,71; 2,01</t>
+          <t>-67,54; 2,04</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-63,34; 43,26</t>
+          <t>-64,87; 39,51</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>37,26; 398,86</t>
+          <t>38,22; 388,29</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-26,03; 206,72</t>
+          <t>-24,87; 229,04</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>80,18; 443,07</t>
+          <t>83,88; 464,26</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,17; 133,2</t>
+          <t>10,11; 138,9</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-41,66; 40,19</t>
+          <t>-42,96; 36,56</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-7,8; 114,79</t>
+          <t>-6,93; 113,08</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,57; 0,32</t>
+          <t>-3,38; 0,32</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,2; 0,5</t>
+          <t>-3,29; 0,38</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,9; 2,08</t>
+          <t>-2,03; 1,96</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,83; 2,35</t>
+          <t>-1,78; 2,2</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,74; 0,91</t>
+          <t>-2,82; 0,87</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-2,31; 2,39</t>
+          <t>-2,38; 2,33</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,94; 0,89</t>
+          <t>-1,89; 0,89</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,48; 0,34</t>
+          <t>-2,39; 0,37</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-1,52; 1,7</t>
+          <t>-1,47; 1,67</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-71,81; 18,93</t>
+          <t>-70,33; 14,93</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-67,55; 22,73</t>
+          <t>-69,86; 22,92</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-40,72; 82,09</t>
+          <t>-42,83; 75,24</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-40,13; 106,34</t>
+          <t>-42,11; 91,73</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-62,01; 41,74</t>
+          <t>-63,33; 37,56</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-48,36; 90,81</t>
+          <t>-51,43; 88,98</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-45,92; 32,89</t>
+          <t>-44,96; 36,08</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-57,41; 13,05</t>
+          <t>-57,23; 16,69</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-34,14; 57,77</t>
+          <t>-34,96; 58,62</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,75; 0,2</t>
+          <t>-3,99; 0,24</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,64; -0,97</t>
+          <t>-4,76; -0,86</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,15; 1,03</t>
+          <t>-3,05; 1,18</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 2,96</t>
+          <t>-1,28; 2,77</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,92; 0,89</t>
+          <t>-2,96; 0,98</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,94; 2,85</t>
+          <t>-1,23; 2,74</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-1,82; 0,93</t>
+          <t>-1,8; 1,09</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-3,28; -0,53</t>
+          <t>-3,23; -0,6</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-1,4; 1,4</t>
+          <t>-1,39; 1,55</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-51,23; 4,98</t>
+          <t>-53,47; 6,23</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-65,72; -17,05</t>
+          <t>-65,4; -12,67</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-43,86; 21,53</t>
+          <t>-42,04; 22,89</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-18,17; 76,15</t>
+          <t>-20,65; 69,69</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-47,79; 21,12</t>
+          <t>-48,22; 24,02</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-15,04; 69,04</t>
+          <t>-19,61; 65,5</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-28,72; 19,24</t>
+          <t>-28,65; 20,96</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-51,18; -10,07</t>
+          <t>-52,67; -11,18</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-22,35; 29,58</t>
+          <t>-22,37; 32,01</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,26; 0,72</t>
+          <t>-1,24; 0,79</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,46; -0,68</t>
+          <t>-2,55; -0,8</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 1,44</t>
+          <t>-0,82; 1,33</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,48; 2,39</t>
+          <t>0,42; 2,3</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-1,03; 0,73</t>
+          <t>-0,97; 0,76</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,99; 3,13</t>
+          <t>1,1; 3,18</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,11; 1,33</t>
+          <t>-0,07; 1,24</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-1,46; -0,2</t>
+          <t>-1,49; -0,21</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,4; 1,98</t>
+          <t>0,38; 1,95</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-27,67; 20,27</t>
+          <t>-26,95; 22,32</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-54,24; -19,28</t>
+          <t>-55,87; -21,45</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-21,01; 39,43</t>
+          <t>-18,74; 36,84</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>13,32; 86,73</t>
+          <t>11,17; 84,88</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-29,49; 27,08</t>
+          <t>-28,0; 27,5</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>28,33; 115,71</t>
+          <t>32,24; 116,92</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-2,91; 41,31</t>
+          <t>-2,03; 37,37</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-37,78; -6,05</t>
+          <t>-38,48; -7,08</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>10,23; 60,35</t>
+          <t>10,12; 58,92</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P3A_R2-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P3A_R2-Habitat-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4,06</t>
+          <t>3,83</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,52</t>
+          <t>5,0</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>4,3</t>
+          <t>4,43</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,47; 3,93</t>
+          <t>0,19; 4,04</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,91; 1,07</t>
+          <t>-1,83; 1,09</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,17; 6,24</t>
+          <t>1,91; 5,89</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,21; 3,99</t>
+          <t>0,2; 3,95</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 2,75</t>
+          <t>-0,71; 2,74</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,59; 6,19</t>
+          <t>3,24; 6,52</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,81; 3,28</t>
+          <t>0,8; 3,4</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 1,48</t>
+          <t>-0,92; 1,44</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,0; 5,59</t>
+          <t>3,24; 5,75</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>181,64%</t>
+          <t>171,23%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>222,17%</t>
+          <t>245,98%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>201,26%</t>
+          <t>207,45%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>10,34; 277,69</t>
+          <t>3,74; 265,67</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-62,24; 76,29</t>
+          <t>-59,37; 81,94</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>60,3; 414,51</t>
+          <t>50,98; 389,37</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,59; 282,62</t>
+          <t>1,41; 290,34</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-35,84; 209,11</t>
+          <t>-31,57; 207,94</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>85,29; 494,52</t>
+          <t>97,11; 501,35</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>30,56; 205,93</t>
+          <t>23,98; 200,9</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-30,98; 88,52</t>
+          <t>-34,6; 88,63</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>107,22; 345,35</t>
+          <t>110,99; 359,45</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-0,66</t>
+          <t>0,15</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,51</t>
+          <t>3,4</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1,31</t>
+          <t>1,79</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 2,38</t>
+          <t>-1,14; 2,36</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,19; -0,02</t>
+          <t>-3,14; 0,05</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,07; 1,15</t>
+          <t>-1,72; 2,12</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,94; 4,1</t>
+          <t>1,08; 4,02</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 2,41</t>
+          <t>-0,54; 2,42</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,14; 4,98</t>
+          <t>2,0; 4,61</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,35; 2,81</t>
+          <t>0,37; 2,67</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 0,76</t>
+          <t>-1,44; 0,63</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-0,24; 2,5</t>
+          <t>0,76; 2,92</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-18,36%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>214,06%</t>
+          <t>207,53%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>49,76%</t>
+          <t>68,13%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-30,83; 86,25</t>
+          <t>-26,03; 88,56</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-67,54; 2,04</t>
+          <t>-66,4; 5,72</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-64,87; 39,51</t>
+          <t>-39,33; 75,82</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>38,22; 388,29</t>
+          <t>42,83; 398,22</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-24,87; 229,04</t>
+          <t>-25,22; 226,97</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>83,88; 464,26</t>
+          <t>75,18; 421,55</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,11; 138,9</t>
+          <t>8,68; 121,62</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-42,96; 36,56</t>
+          <t>-45,56; 29,8</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-6,93; 113,08</t>
+          <t>22,83; 141,57</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0,15</t>
+          <t>0,25</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,4</t>
+          <t>1,61</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0,27</t>
+          <t>0,93</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,38; 0,32</t>
+          <t>-3,37; 0,39</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,29; 0,38</t>
+          <t>-3,27; 0,5</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,03; 1,96</t>
+          <t>-1,77; 2,36</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,78; 2,2</t>
+          <t>-1,55; 2,53</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,82; 0,87</t>
+          <t>-2,79; 1,1</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-2,38; 2,33</t>
+          <t>-0,36; 3,3</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,89; 0,89</t>
+          <t>-1,9; 0,89</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,39; 0,37</t>
+          <t>-2,44; 0,1</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-1,47; 1,67</t>
+          <t>-0,34; 2,37</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>48,08%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>26,69%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-70,33; 14,93</t>
+          <t>-70,61; 18,01</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-69,86; 22,92</t>
+          <t>-68,58; 22,19</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-42,83; 75,24</t>
+          <t>-38,13; 93,18</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-42,11; 91,73</t>
+          <t>-38,18; 114,94</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-63,33; 37,56</t>
+          <t>-62,6; 51,19</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-51,43; 88,98</t>
+          <t>-10,34; 135,57</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-44,96; 36,08</t>
+          <t>-43,93; 30,09</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-57,23; 16,69</t>
+          <t>-57,23; 6,03</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-34,96; 58,62</t>
+          <t>-8,08; 84,31</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-1,01</t>
+          <t>-1,17</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,95</t>
+          <t>1,31</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>0,03</t>
+          <t>0,14</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,99; 0,24</t>
+          <t>-3,65; 0,24</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,76; -0,86</t>
+          <t>-4,81; -1,1</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,05; 1,18</t>
+          <t>-3,24; 0,98</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,28; 2,77</t>
+          <t>-1,17; 3,21</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,96; 0,98</t>
+          <t>-2,95; 0,84</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,23; 2,74</t>
+          <t>-0,68; 3,03</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-1,8; 1,09</t>
+          <t>-1,97; 1,03</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-3,23; -0,6</t>
+          <t>-3,31; -0,58</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 1,55</t>
+          <t>-1,14; 1,56</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-16,6%</t>
+          <t>-19,27%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>25,36%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>2,46%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-53,47; 6,23</t>
+          <t>-52,49; 5,38</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-65,4; -12,67</t>
+          <t>-67,64; -20,22</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-42,04; 22,89</t>
+          <t>-44,44; 20,09</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-20,65; 69,69</t>
+          <t>-19,08; 78,8</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-48,22; 24,02</t>
+          <t>-49,56; 20,11</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-19,61; 65,5</t>
+          <t>-11,0; 76,09</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-28,65; 20,96</t>
+          <t>-30,53; 21,49</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-52,67; -11,18</t>
+          <t>-52,5; -11,77</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-22,37; 32,01</t>
+          <t>-18,44; 34,45</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>0,27</t>
+          <t>0,53</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,21</t>
+          <t>2,7</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>1,26</t>
+          <t>1,64</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 0,79</t>
+          <t>-1,18; 0,78</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,55; -0,8</t>
+          <t>-2,43; -0,78</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 1,33</t>
+          <t>-0,61; 1,5</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,42; 2,3</t>
+          <t>0,49; 2,34</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,97; 0,76</t>
+          <t>-0,91; 0,85</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,1; 3,18</t>
+          <t>1,76; 3,54</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,07; 1,24</t>
+          <t>-0,07; 1,32</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-1,49; -0,21</t>
+          <t>-1,42; -0,22</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,38; 1,95</t>
+          <t>0,96; 2,25</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>70,03%</t>
+          <t>85,59%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>35,13%</t>
+          <t>45,58%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-26,95; 22,32</t>
+          <t>-26,62; 22,06</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-55,87; -21,45</t>
+          <t>-53,62; -20,36</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-18,74; 36,84</t>
+          <t>-13,09; 41,45</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>11,17; 84,88</t>
+          <t>13,0; 85,3</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-28,0; 27,5</t>
+          <t>-25,83; 32,47</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>32,24; 116,92</t>
+          <t>46,96; 129,73</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-2,03; 37,37</t>
+          <t>-1,86; 38,92</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-38,48; -7,08</t>
+          <t>-36,96; -6,87</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>10,12; 58,92</t>
+          <t>23,91; 68,6</t>
         </is>
       </c>
     </row>
